--- a/INF_ALP_2025.xlsx
+++ b/INF_ALP_2025.xlsx
@@ -379,415 +379,421 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
+      <c r="A2" s="1" t="n">
         <v>202411909648</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="0" t="n">
+      <c r="C2" s="1" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
+      <c r="A3" s="1" t="n">
         <v>202511602542</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="0" t="n">
+      <c r="C3" s="1" t="n">
         <v>2</v>
       </c>
       <c r="D3" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
+      <c r="A4" s="1" t="n">
         <v>202511602545</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="n">
+      <c r="A5" s="1" t="n">
         <v>202511603200</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="0" t="n">
+      <c r="C5" s="1" t="n">
         <v>4</v>
       </c>
       <c r="D5" s="2"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="n">
+      <c r="A6" s="1" t="n">
         <v>202511602497</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="0" t="n">
+      <c r="C6" s="1" t="n">
         <v>10</v>
       </c>
       <c r="D6" s="2"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="n">
+      <c r="A7" s="1" t="n">
         <v>202511602473</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="0" t="n">
+      <c r="C7" s="1" t="n">
         <v>8</v>
       </c>
       <c r="D7" s="2"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="n">
+      <c r="A8" s="1" t="n">
         <v>202511602524</v>
       </c>
-      <c r="B8" s="0" t="s">
-        <v>10</v>
+      <c r="B8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="n">
+      <c r="A9" s="1" t="n">
         <v>202511602491</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B9" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="0" t="n">
+      <c r="C9" s="1" t="n">
         <v>2</v>
       </c>
       <c r="D9" s="2"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="n">
+      <c r="A10" s="1" t="n">
         <v>202511602441</v>
       </c>
-      <c r="B10" s="0" t="s">
+      <c r="B10" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="0" t="n">
+      <c r="C10" s="1" t="n">
         <v>10</v>
       </c>
       <c r="D10" s="2"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="n">
+      <c r="A11" s="1" t="n">
         <v>202511602567</v>
       </c>
-      <c r="B11" s="0" t="s">
+      <c r="B11" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C11" s="0" t="n">
+      <c r="C11" s="1" t="n">
         <v>2</v>
       </c>
       <c r="D11" s="2"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="n">
+      <c r="A12" s="1" t="n">
         <v>202511602557</v>
       </c>
-      <c r="B12" s="0" t="s">
+      <c r="B12" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="0" t="n">
+      <c r="C12" s="1" t="n">
         <v>10</v>
       </c>
       <c r="D12" s="2"/>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="n">
+      <c r="A13" s="1" t="n">
         <v>202511602452</v>
       </c>
-      <c r="B13" s="0" t="s">
+      <c r="B13" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C13" s="0" t="n">
+      <c r="C13" s="1" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="n">
+      <c r="A14" s="1" t="n">
         <v>202511603204</v>
       </c>
-      <c r="B14" s="0" t="s">
+      <c r="B14" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C14" s="0" t="n">
+      <c r="C14" s="1" t="n">
         <v>2</v>
       </c>
       <c r="D14" s="2"/>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="n">
+      <c r="A15" s="1" t="n">
         <v>202511603162</v>
       </c>
-      <c r="B15" s="0" t="s">
+      <c r="B15" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C15" s="0" t="n">
+      <c r="C15" s="1" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="n">
+      <c r="A16" s="1" t="n">
         <v>202511602437</v>
       </c>
-      <c r="B16" s="0" t="s">
+      <c r="B16" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="C16" s="0" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="n">
+      <c r="A17" s="1" t="n">
         <v>202511602537</v>
       </c>
-      <c r="B17" s="0" t="s">
+      <c r="B17" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C17" s="0" t="n">
+      <c r="C17" s="1" t="n">
         <v>8</v>
       </c>
       <c r="D17" s="2"/>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="n">
+      <c r="A18" s="1" t="n">
         <v>202511602501</v>
       </c>
-      <c r="B18" s="0" t="s">
+      <c r="B18" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C18" s="0" t="n">
+      <c r="C18" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="n">
+      <c r="A19" s="1" t="n">
         <v>202511603157</v>
       </c>
-      <c r="B19" s="0" t="s">
+      <c r="B19" s="1" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="n">
+      <c r="A20" s="1" t="n">
         <v>202511603167</v>
       </c>
-      <c r="B20" s="0" t="s">
+      <c r="B20" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C20" s="0" t="n">
+      <c r="C20" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="n">
+      <c r="A21" s="1" t="n">
         <v>202511602444</v>
       </c>
-      <c r="B21" s="0" t="s">
+      <c r="B21" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C21" s="0" t="n">
+      <c r="C21" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="n">
+      <c r="A22" s="1" t="n">
         <v>202511602349</v>
       </c>
-      <c r="B22" s="0" t="s">
+      <c r="B22" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C22" s="0" t="n">
+      <c r="C22" s="1" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="n">
+      <c r="A23" s="1" t="n">
         <v>202511602536</v>
       </c>
-      <c r="B23" s="0" t="s">
+      <c r="B23" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C23" s="0" t="n">
+      <c r="C23" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="n">
+      <c r="A24" s="1" t="n">
         <v>202511602440</v>
       </c>
-      <c r="B24" s="0" t="s">
+      <c r="B24" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C24" s="0" t="n">
+      <c r="C24" s="1" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="n">
+      <c r="A25" s="1" t="n">
         <v>202511602492</v>
       </c>
-      <c r="B25" s="0" t="s">
+      <c r="B25" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C25" s="0" t="n">
+      <c r="C25" s="1" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="n">
+      <c r="A26" s="1" t="n">
         <v>202511602456</v>
       </c>
-      <c r="B26" s="0" t="s">
+      <c r="B26" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C26" s="0" t="n">
+      <c r="C26" s="1" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="n">
+      <c r="A27" s="1" t="n">
         <v>202511603158</v>
       </c>
-      <c r="B27" s="0" t="s">
+      <c r="B27" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C27" s="0" t="n">
+      <c r="C27" s="1" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0" t="n">
+      <c r="A28" s="1" t="n">
         <v>202511602455</v>
       </c>
-      <c r="B28" s="0" t="s">
+      <c r="B28" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C28" s="0" t="n">
+      <c r="C28" s="1" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="0" t="n">
+      <c r="A29" s="1" t="n">
         <v>202511602443</v>
       </c>
-      <c r="B29" s="0" t="s">
+      <c r="B29" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C29" s="0" t="n">
+      <c r="C29" s="1" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="0" t="n">
+      <c r="A30" s="1" t="n">
         <v>202511602464</v>
       </c>
-      <c r="B30" s="0" t="s">
+      <c r="B30" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C30" s="0" t="n">
+      <c r="C30" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="0" t="n">
+      <c r="A31" s="1" t="n">
         <v>202511602459</v>
       </c>
-      <c r="B31" s="0" t="s">
+      <c r="B31" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C31" s="0" t="n">
+      <c r="C31" s="1" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="0" t="n">
+      <c r="A32" s="1" t="n">
         <v>202511602519</v>
       </c>
-      <c r="B32" s="0" t="s">
+      <c r="B32" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C32" s="0" t="n">
-        <v>10</v>
+      <c r="C32" s="1" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="0" t="n">
+      <c r="A33" s="1" t="n">
         <v>202511602519</v>
       </c>
-      <c r="B33" s="0" t="s">
+      <c r="B33" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C33" s="0" t="n">
+      <c r="C33" s="1" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="0" t="n">
+      <c r="A34" s="1" t="n">
         <v>202511602569</v>
       </c>
-      <c r="B34" s="0" t="s">
+      <c r="B34" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C34" s="0" t="n">
+      <c r="C34" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="0" t="n">
+      <c r="A35" s="1" t="n">
         <v>202511602470</v>
       </c>
-      <c r="B35" s="0" t="s">
+      <c r="B35" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C35" s="0" t="n">
+      <c r="C35" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="0" t="n">
+      <c r="A36" s="1" t="n">
         <v>202511602510</v>
       </c>
-      <c r="B36" s="0" t="s">
+      <c r="B36" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C36" s="0" t="n">
+      <c r="C36" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="0" t="n">
+      <c r="A37" s="1" t="n">
         <v>202511602518</v>
       </c>
-      <c r="B37" s="0" t="s">
+      <c r="B37" s="1" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="0" t="n">
+      <c r="A38" s="1" t="n">
         <v>202511602530</v>
       </c>
-      <c r="B38" s="0" t="s">
+      <c r="B38" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C38" s="0" t="n">
+      <c r="C38" s="1" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="0" t="n">
+      <c r="A39" s="1" t="n">
         <v>202511602513</v>
       </c>
-      <c r="B39" s="0" t="s">
+      <c r="B39" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C39" s="0" t="n">
+      <c r="C39" s="1" t="n">
         <v>8</v>
       </c>
     </row>

--- a/INF_ALP_2025.xlsx
+++ b/INF_ALP_2025.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
   <si>
     <t xml:space="preserve">Matricula</t>
   </si>
@@ -32,6 +32,24 @@
   </si>
   <si>
     <t xml:space="preserve">Recuperação 01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avaliação 02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recuperação 02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avaliação 03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recuperação 03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avaliação 04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recuperação 04</t>
   </si>
   <si>
     <t xml:space="preserve">ALEXSANDRO SOUZA DA SILVA</t>
@@ -356,12 +374,14 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D39"/>
+  <dimension ref="A1:J39"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14.53"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="44.34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="15.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="15.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="15.72"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -377,425 +397,662 @@
       <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="n">
         <v>202411909648</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C2" s="1" t="n">
         <v>10</v>
       </c>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="n">
         <v>202511602542</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C3" s="1" t="n">
         <v>2</v>
       </c>
       <c r="D3" s="2"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="1"/>
+      <c r="J3" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="n">
         <v>202511602545</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="F4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="J4" s="1"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="n">
         <v>202511603200</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C5" s="1" t="n">
         <v>4</v>
       </c>
       <c r="D5" s="2"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="1"/>
+      <c r="J5" s="2"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="n">
         <v>202511602497</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C6" s="1" t="n">
         <v>10</v>
       </c>
       <c r="D6" s="2"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="2"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="n">
         <v>202511602473</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C7" s="1" t="n">
         <v>8</v>
       </c>
       <c r="D7" s="2"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="1"/>
+      <c r="J7" s="2"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="n">
         <v>202511602524</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" s="0" t="n">
-        <v>0</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="C8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
+      <c r="J8" s="1"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="n">
         <v>202511602491</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C9" s="1" t="n">
         <v>2</v>
       </c>
       <c r="D9" s="2"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="1"/>
+      <c r="J9" s="2"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="n">
         <v>202511602441</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C10" s="1" t="n">
         <v>10</v>
       </c>
       <c r="D10" s="2"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="1"/>
+      <c r="J10" s="2"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="n">
         <v>202511602567</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C11" s="1" t="n">
         <v>2</v>
       </c>
       <c r="D11" s="2"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="1"/>
+      <c r="J11" s="2"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="n">
         <v>202511602557</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C12" s="1" t="n">
         <v>10</v>
       </c>
       <c r="D12" s="2"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="1"/>
+      <c r="J12" s="2"/>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="n">
         <v>202511602452</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C13" s="1" t="n">
         <v>8</v>
       </c>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
+      <c r="J13" s="1"/>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="n">
         <v>202511603204</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C14" s="1" t="n">
         <v>2</v>
       </c>
       <c r="D14" s="2"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="1"/>
+      <c r="J14" s="2"/>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="n">
         <v>202511603162</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="C15" s="1" t="n">
         <v>2</v>
       </c>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
+      <c r="J15" s="1"/>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="n">
         <v>202511602437</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C16" s="0" t="n">
-        <v>0</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="C16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1"/>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="n">
         <v>202511602537</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C17" s="1" t="n">
         <v>8</v>
       </c>
       <c r="D17" s="2"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="1"/>
+      <c r="J17" s="2"/>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="n">
         <v>202511602501</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C18" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
+      <c r="I18" s="1"/>
+      <c r="J18" s="1"/>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="n">
         <v>202511603157</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>21</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="F19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="J19" s="1"/>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="n">
         <v>202511603167</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C20" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
+      <c r="J20" s="1"/>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="n">
         <v>202511602444</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C21" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
+      <c r="I21" s="1"/>
+      <c r="J21" s="1"/>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="n">
         <v>202511602349</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C22" s="1" t="n">
         <v>10</v>
       </c>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
+      <c r="I22" s="1"/>
+      <c r="J22" s="1"/>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="n">
         <v>202511602536</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C23" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
+      <c r="G23" s="1"/>
+      <c r="H23" s="1"/>
+      <c r="I23" s="1"/>
+      <c r="J23" s="1"/>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="n">
         <v>202511602440</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C24" s="1" t="n">
         <v>6</v>
       </c>
+      <c r="E24" s="1"/>
+      <c r="F24" s="1"/>
+      <c r="G24" s="1"/>
+      <c r="H24" s="1"/>
+      <c r="I24" s="1"/>
+      <c r="J24" s="1"/>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="n">
         <v>202511602492</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C25" s="1" t="n">
         <v>10</v>
       </c>
+      <c r="E25" s="1"/>
+      <c r="F25" s="1"/>
+      <c r="G25" s="1"/>
+      <c r="H25" s="1"/>
+      <c r="I25" s="1"/>
+      <c r="J25" s="1"/>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="n">
         <v>202511602456</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C26" s="1" t="n">
         <v>10</v>
       </c>
+      <c r="E26" s="1"/>
+      <c r="F26" s="1"/>
+      <c r="G26" s="1"/>
+      <c r="H26" s="1"/>
+      <c r="I26" s="1"/>
+      <c r="J26" s="1"/>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="n">
         <v>202511603158</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="C27" s="1" t="n">
         <v>10</v>
       </c>
+      <c r="E27" s="1"/>
+      <c r="F27" s="1"/>
+      <c r="G27" s="1"/>
+      <c r="H27" s="1"/>
+      <c r="I27" s="1"/>
+      <c r="J27" s="1"/>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="n">
         <v>202511602455</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C28" s="1" t="n">
         <v>2</v>
       </c>
+      <c r="E28" s="1"/>
+      <c r="F28" s="1"/>
+      <c r="G28" s="1"/>
+      <c r="H28" s="1"/>
+      <c r="I28" s="1"/>
+      <c r="J28" s="1"/>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="n">
         <v>202511602443</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="C29" s="1" t="n">
         <v>2</v>
       </c>
+      <c r="E29" s="1"/>
+      <c r="F29" s="1"/>
+      <c r="G29" s="1"/>
+      <c r="H29" s="1"/>
+      <c r="I29" s="1"/>
+      <c r="J29" s="1"/>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="n">
         <v>202511602464</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C30" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="E30" s="1"/>
+      <c r="F30" s="1"/>
+      <c r="G30" s="1"/>
+      <c r="H30" s="1"/>
+      <c r="I30" s="1"/>
+      <c r="J30" s="1"/>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="n">
         <v>202511602459</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="C31" s="1" t="n">
         <v>8</v>
       </c>
+      <c r="E31" s="1"/>
+      <c r="F31" s="1"/>
+      <c r="G31" s="1"/>
+      <c r="H31" s="1"/>
+      <c r="I31" s="1"/>
+      <c r="J31" s="1"/>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="n">
         <v>202511602519</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C32" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="E32" s="1"/>
+      <c r="F32" s="1"/>
+      <c r="G32" s="1"/>
+      <c r="H32" s="1"/>
+      <c r="I32" s="1"/>
+      <c r="J32" s="1"/>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="n">
         <v>202511602519</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="C33" s="1" t="n">
         <v>10</v>
       </c>
+      <c r="E33" s="1"/>
+      <c r="F33" s="1"/>
+      <c r="G33" s="1"/>
+      <c r="H33" s="1"/>
+      <c r="I33" s="1"/>
+      <c r="J33" s="1"/>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="n">
         <v>202511602569</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C34" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="E34" s="1"/>
+      <c r="F34" s="1"/>
+      <c r="G34" s="1"/>
+      <c r="H34" s="1"/>
+      <c r="I34" s="1"/>
+      <c r="J34" s="1"/>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="n">
         <v>202511602470</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C35" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="E35" s="1"/>
+      <c r="F35" s="1"/>
+      <c r="G35" s="1"/>
+      <c r="H35" s="1"/>
+      <c r="I35" s="1"/>
+      <c r="J35" s="1"/>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="n">
         <v>202511602510</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C36" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="E36" s="1"/>
+      <c r="F36" s="1"/>
+      <c r="G36" s="1"/>
+      <c r="H36" s="1"/>
+      <c r="I36" s="1"/>
+      <c r="J36" s="1"/>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="n">
         <v>202511602518</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>39</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="F37" s="1"/>
+      <c r="H37" s="1"/>
+      <c r="J37" s="1"/>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="n">
         <v>202511602530</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="C38" s="1" t="n">
         <v>4</v>
       </c>
+      <c r="E38" s="1"/>
+      <c r="F38" s="1"/>
+      <c r="G38" s="1"/>
+      <c r="H38" s="1"/>
+      <c r="I38" s="1"/>
+      <c r="J38" s="1"/>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="n">
         <v>202511602513</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C39" s="1" t="n">
         <v>8</v>
       </c>
+      <c r="E39" s="1"/>
+      <c r="F39" s="1"/>
+      <c r="G39" s="1"/>
+      <c r="H39" s="1"/>
+      <c r="I39" s="1"/>
+      <c r="J39" s="1"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/INF_ALP_2025.xlsx
+++ b/INF_ALP_2025.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
   <si>
     <t xml:space="preserve">Matricula</t>
   </si>
@@ -32,24 +32,6 @@
   </si>
   <si>
     <t xml:space="preserve">Recuperação 01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Avaliação 02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recuperação 02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Avaliação 03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recuperação 03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Avaliação 04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recuperação 04</t>
   </si>
   <si>
     <t xml:space="preserve">ALEXSANDRO SOUZA DA SILVA</t>
@@ -397,31 +379,19 @@
       <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>9</v>
-      </c>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="n">
         <v>202411909648</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C2" s="1" t="n">
         <v>10</v>
@@ -438,7 +408,7 @@
         <v>202511602542</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C3" s="1" t="n">
         <v>2</v>
@@ -456,7 +426,7 @@
         <v>202511602545</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F4" s="1"/>
       <c r="H4" s="1"/>
@@ -467,7 +437,7 @@
         <v>202511603200</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C5" s="1" t="n">
         <v>4</v>
@@ -485,7 +455,7 @@
         <v>202511602497</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C6" s="1" t="n">
         <v>10</v>
@@ -503,7 +473,7 @@
         <v>202511602473</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C7" s="1" t="n">
         <v>8</v>
@@ -521,7 +491,7 @@
         <v>202511602524</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C8" s="1" t="n">
         <v>0</v>
@@ -538,7 +508,7 @@
         <v>202511602491</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C9" s="1" t="n">
         <v>2</v>
@@ -556,7 +526,7 @@
         <v>202511602441</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C10" s="1" t="n">
         <v>10</v>
@@ -574,7 +544,7 @@
         <v>202511602567</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C11" s="1" t="n">
         <v>2</v>
@@ -592,7 +562,7 @@
         <v>202511602557</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C12" s="1" t="n">
         <v>10</v>
@@ -610,7 +580,7 @@
         <v>202511602452</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C13" s="1" t="n">
         <v>8</v>
@@ -627,7 +597,7 @@
         <v>202511603204</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="C14" s="1" t="n">
         <v>2</v>
@@ -645,7 +615,7 @@
         <v>202511603162</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C15" s="1" t="n">
         <v>2</v>
@@ -662,7 +632,7 @@
         <v>202511602437</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C16" s="1" t="n">
         <v>0</v>
@@ -679,7 +649,7 @@
         <v>202511602537</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="C17" s="1" t="n">
         <v>8</v>
@@ -697,7 +667,7 @@
         <v>202511602501</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C18" s="1" t="n">
         <v>0</v>
@@ -714,7 +684,7 @@
         <v>202511603157</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="F19" s="1"/>
       <c r="H19" s="1"/>
@@ -725,7 +695,7 @@
         <v>202511603167</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C20" s="1" t="n">
         <v>0</v>
@@ -742,7 +712,7 @@
         <v>202511602444</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C21" s="1" t="n">
         <v>0</v>
@@ -759,7 +729,7 @@
         <v>202511602349</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C22" s="1" t="n">
         <v>10</v>
@@ -776,7 +746,7 @@
         <v>202511602536</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C23" s="1" t="n">
         <v>0</v>
@@ -793,7 +763,7 @@
         <v>202511602440</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="C24" s="1" t="n">
         <v>6</v>
@@ -810,7 +780,7 @@
         <v>202511602492</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="C25" s="1" t="n">
         <v>10</v>
@@ -827,7 +797,7 @@
         <v>202511602456</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C26" s="1" t="n">
         <v>10</v>
@@ -844,7 +814,7 @@
         <v>202511603158</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C27" s="1" t="n">
         <v>10</v>
@@ -861,7 +831,7 @@
         <v>202511602455</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C28" s="1" t="n">
         <v>2</v>
@@ -878,7 +848,7 @@
         <v>202511602443</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="C29" s="1" t="n">
         <v>2</v>
@@ -895,7 +865,7 @@
         <v>202511602464</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="C30" s="1" t="n">
         <v>0</v>
@@ -912,7 +882,7 @@
         <v>202511602459</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="C31" s="1" t="n">
         <v>8</v>
@@ -929,7 +899,7 @@
         <v>202511602519</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="C32" s="1" t="n">
         <v>0</v>
@@ -946,7 +916,7 @@
         <v>202511602519</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="C33" s="1" t="n">
         <v>10</v>
@@ -963,7 +933,7 @@
         <v>202511602569</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="C34" s="1" t="n">
         <v>0</v>
@@ -980,7 +950,7 @@
         <v>202511602470</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C35" s="1" t="n">
         <v>0</v>
@@ -997,7 +967,7 @@
         <v>202511602510</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="C36" s="1" t="n">
         <v>0</v>
@@ -1014,7 +984,7 @@
         <v>202511602518</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="F37" s="1"/>
       <c r="H37" s="1"/>
@@ -1025,7 +995,7 @@
         <v>202511602530</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="C38" s="1" t="n">
         <v>4</v>
@@ -1042,7 +1012,7 @@
         <v>202511602513</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C39" s="1" t="n">
         <v>8</v>

--- a/INF_ALP_2025.xlsx
+++ b/INF_ALP_2025.xlsx
@@ -362,8 +362,8 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14.53"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="44.34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="15.72"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="15.72"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="15.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="15.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="15.72"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -397,9 +397,7 @@
         <v>10</v>
       </c>
       <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
       <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
     </row>
@@ -413,7 +411,9 @@
       <c r="C3" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="D3" s="2"/>
+      <c r="D3" s="2" t="n">
+        <v>4</v>
+      </c>
       <c r="E3" s="1"/>
       <c r="F3" s="2"/>
       <c r="G3" s="1"/>
@@ -428,8 +428,9 @@
       <c r="B4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="1"/>
-      <c r="H4" s="1"/>
+      <c r="D4" s="1" t="n">
+        <v>6</v>
+      </c>
       <c r="J4" s="1"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -442,7 +443,9 @@
       <c r="C5" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="D5" s="2"/>
+      <c r="D5" s="2" t="n">
+        <v>10</v>
+      </c>
       <c r="E5" s="1"/>
       <c r="F5" s="2"/>
       <c r="G5" s="1"/>
@@ -478,7 +481,9 @@
       <c r="C7" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="D7" s="2"/>
+      <c r="D7" s="2" t="n">
+        <v>10</v>
+      </c>
       <c r="E7" s="1"/>
       <c r="F7" s="2"/>
       <c r="G7" s="1"/>
@@ -496,10 +501,11 @@
       <c r="C8" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="D8" s="1" t="n">
+        <v>0</v>
+      </c>
       <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
       <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
     </row>
@@ -513,7 +519,9 @@
       <c r="C9" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="D9" s="2"/>
+      <c r="D9" s="2" t="n">
+        <v>10</v>
+      </c>
       <c r="E9" s="1"/>
       <c r="F9" s="2"/>
       <c r="G9" s="1"/>
@@ -549,7 +557,9 @@
       <c r="C11" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="D11" s="2"/>
+      <c r="D11" s="2" t="n">
+        <v>2</v>
+      </c>
       <c r="E11" s="1"/>
       <c r="F11" s="2"/>
       <c r="G11" s="1"/>
@@ -586,9 +596,7 @@
         <v>8</v>
       </c>
       <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
       <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
     </row>
@@ -602,7 +610,9 @@
       <c r="C14" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="D14" s="2"/>
+      <c r="D14" s="2" t="n">
+        <v>4</v>
+      </c>
       <c r="E14" s="1"/>
       <c r="F14" s="2"/>
       <c r="G14" s="1"/>
@@ -620,10 +630,11 @@
       <c r="C15" s="1" t="n">
         <v>2</v>
       </c>
+      <c r="D15" s="1" t="n">
+        <v>6</v>
+      </c>
       <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
       <c r="G15" s="1"/>
-      <c r="H15" s="1"/>
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
     </row>
@@ -638,9 +649,7 @@
         <v>0</v>
       </c>
       <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
       <c r="G16" s="1"/>
-      <c r="H16" s="1"/>
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
     </row>
@@ -672,10 +681,11 @@
       <c r="C18" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="D18" s="1" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="1"/>
-      <c r="F18" s="1"/>
       <c r="G18" s="1"/>
-      <c r="H18" s="1"/>
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
     </row>
@@ -686,8 +696,9 @@
       <c r="B19" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F19" s="1"/>
-      <c r="H19" s="1"/>
+      <c r="D19" s="1" t="n">
+        <v>8</v>
+      </c>
       <c r="J19" s="1"/>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -700,10 +711,11 @@
       <c r="C20" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="D20" s="1" t="n">
+        <v>4</v>
+      </c>
       <c r="E20" s="1"/>
-      <c r="F20" s="1"/>
       <c r="G20" s="1"/>
-      <c r="H20" s="1"/>
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
     </row>
@@ -717,10 +729,11 @@
       <c r="C21" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="D21" s="1" t="n">
+        <v>2</v>
+      </c>
       <c r="E21" s="1"/>
-      <c r="F21" s="1"/>
       <c r="G21" s="1"/>
-      <c r="H21" s="1"/>
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
     </row>
@@ -735,9 +748,7 @@
         <v>10</v>
       </c>
       <c r="E22" s="1"/>
-      <c r="F22" s="1"/>
       <c r="G22" s="1"/>
-      <c r="H22" s="1"/>
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
     </row>
@@ -751,10 +762,11 @@
       <c r="C23" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="D23" s="1" t="n">
+        <v>8</v>
+      </c>
       <c r="E23" s="1"/>
-      <c r="F23" s="1"/>
       <c r="G23" s="1"/>
-      <c r="H23" s="1"/>
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
     </row>
@@ -768,10 +780,11 @@
       <c r="C24" s="1" t="n">
         <v>6</v>
       </c>
+      <c r="D24" s="1" t="n">
+        <v>6</v>
+      </c>
       <c r="E24" s="1"/>
-      <c r="F24" s="1"/>
       <c r="G24" s="1"/>
-      <c r="H24" s="1"/>
       <c r="I24" s="1"/>
       <c r="J24" s="1"/>
     </row>
@@ -786,9 +799,7 @@
         <v>10</v>
       </c>
       <c r="E25" s="1"/>
-      <c r="F25" s="1"/>
       <c r="G25" s="1"/>
-      <c r="H25" s="1"/>
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
     </row>
@@ -803,9 +814,7 @@
         <v>10</v>
       </c>
       <c r="E26" s="1"/>
-      <c r="F26" s="1"/>
       <c r="G26" s="1"/>
-      <c r="H26" s="1"/>
       <c r="I26" s="1"/>
       <c r="J26" s="1"/>
     </row>
@@ -820,9 +829,7 @@
         <v>10</v>
       </c>
       <c r="E27" s="1"/>
-      <c r="F27" s="1"/>
       <c r="G27" s="1"/>
-      <c r="H27" s="1"/>
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
     </row>
@@ -836,10 +843,11 @@
       <c r="C28" s="1" t="n">
         <v>2</v>
       </c>
+      <c r="D28" s="1" t="n">
+        <v>6</v>
+      </c>
       <c r="E28" s="1"/>
-      <c r="F28" s="1"/>
       <c r="G28" s="1"/>
-      <c r="H28" s="1"/>
       <c r="I28" s="1"/>
       <c r="J28" s="1"/>
     </row>
@@ -854,9 +862,7 @@
         <v>2</v>
       </c>
       <c r="E29" s="1"/>
-      <c r="F29" s="1"/>
       <c r="G29" s="1"/>
-      <c r="H29" s="1"/>
       <c r="I29" s="1"/>
       <c r="J29" s="1"/>
     </row>
@@ -871,9 +877,7 @@
         <v>0</v>
       </c>
       <c r="E30" s="1"/>
-      <c r="F30" s="1"/>
       <c r="G30" s="1"/>
-      <c r="H30" s="1"/>
       <c r="I30" s="1"/>
       <c r="J30" s="1"/>
     </row>
@@ -887,10 +891,11 @@
       <c r="C31" s="1" t="n">
         <v>8</v>
       </c>
+      <c r="D31" s="1" t="n">
+        <v>4</v>
+      </c>
       <c r="E31" s="1"/>
-      <c r="F31" s="1"/>
       <c r="G31" s="1"/>
-      <c r="H31" s="1"/>
       <c r="I31" s="1"/>
       <c r="J31" s="1"/>
     </row>
@@ -904,10 +909,11 @@
       <c r="C32" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="D32" s="1" t="n">
+        <v>0</v>
+      </c>
       <c r="E32" s="1"/>
-      <c r="F32" s="1"/>
       <c r="G32" s="1"/>
-      <c r="H32" s="1"/>
       <c r="I32" s="1"/>
       <c r="J32" s="1"/>
     </row>
@@ -922,9 +928,7 @@
         <v>10</v>
       </c>
       <c r="E33" s="1"/>
-      <c r="F33" s="1"/>
       <c r="G33" s="1"/>
-      <c r="H33" s="1"/>
       <c r="I33" s="1"/>
       <c r="J33" s="1"/>
     </row>
@@ -938,10 +942,11 @@
       <c r="C34" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="D34" s="1" t="n">
+        <v>0</v>
+      </c>
       <c r="E34" s="1"/>
-      <c r="F34" s="1"/>
       <c r="G34" s="1"/>
-      <c r="H34" s="1"/>
       <c r="I34" s="1"/>
       <c r="J34" s="1"/>
     </row>
@@ -955,10 +960,11 @@
       <c r="C35" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="D35" s="1" t="n">
+        <v>10</v>
+      </c>
       <c r="E35" s="1"/>
-      <c r="F35" s="1"/>
       <c r="G35" s="1"/>
-      <c r="H35" s="1"/>
       <c r="I35" s="1"/>
       <c r="J35" s="1"/>
     </row>
@@ -972,10 +978,11 @@
       <c r="C36" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="D36" s="1" t="n">
+        <v>2</v>
+      </c>
       <c r="E36" s="1"/>
-      <c r="F36" s="1"/>
       <c r="G36" s="1"/>
-      <c r="H36" s="1"/>
       <c r="I36" s="1"/>
       <c r="J36" s="1"/>
     </row>
@@ -986,8 +993,9 @@
       <c r="B37" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="F37" s="1"/>
-      <c r="H37" s="1"/>
+      <c r="D37" s="1" t="n">
+        <v>6</v>
+      </c>
       <c r="J37" s="1"/>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1000,10 +1008,11 @@
       <c r="C38" s="1" t="n">
         <v>4</v>
       </c>
+      <c r="D38" s="1" t="n">
+        <v>2</v>
+      </c>
       <c r="E38" s="1"/>
-      <c r="F38" s="1"/>
       <c r="G38" s="1"/>
-      <c r="H38" s="1"/>
       <c r="I38" s="1"/>
       <c r="J38" s="1"/>
     </row>
@@ -1017,10 +1026,11 @@
       <c r="C39" s="1" t="n">
         <v>8</v>
       </c>
+      <c r="D39" s="1" t="n">
+        <v>10</v>
+      </c>
       <c r="E39" s="1"/>
-      <c r="F39" s="1"/>
       <c r="G39" s="1"/>
-      <c r="H39" s="1"/>
       <c r="I39" s="1"/>
       <c r="J39" s="1"/>
     </row>

--- a/INF_ALP_2025.xlsx
+++ b/INF_ALP_2025.xlsx
@@ -428,6 +428,9 @@
       <c r="B4" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="C4" s="0" t="n">
+        <v>8</v>
+      </c>
       <c r="D4" s="1" t="n">
         <v>6</v>
       </c>

--- a/INF_ALP_2025.xlsx
+++ b/INF_ALP_2025.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
   <si>
     <t xml:space="preserve">Matricula</t>
   </si>
@@ -34,6 +34,12 @@
     <t xml:space="preserve">Recuperação 01</t>
   </si>
   <si>
+    <t xml:space="preserve">Avaliação 02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recuperação 02</t>
+  </si>
+  <si>
     <t xml:space="preserve">ALEXSANDRO SOUZA DA SILVA</t>
   </si>
   <si>
@@ -77,9 +83,6 @@
   </si>
   <si>
     <t xml:space="preserve">JOAO PEDRO MURADAS SOARES</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JOSE PEDRO RAMOS</t>
   </si>
   <si>
     <t xml:space="preserve">JULIA ZULIAN DE LIMA</t>
@@ -356,7 +359,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J39"/>
+  <dimension ref="A1:J38"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14.53"/>
@@ -379,8 +382,12 @@
       <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
@@ -391,12 +398,13 @@
         <v>202411909648</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C2" s="1" t="n">
         <v>10</v>
       </c>
       <c r="E2" s="1"/>
+      <c r="F2" s="0"/>
       <c r="G2" s="1"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
@@ -406,7 +414,7 @@
         <v>202511602542</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C3" s="1" t="n">
         <v>2</v>
@@ -414,8 +422,12 @@
       <c r="D3" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E3" s="1"/>
-      <c r="F3" s="2"/>
+      <c r="E3" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="F3" s="1" t="n">
+        <v>6</v>
+      </c>
       <c r="G3" s="1"/>
       <c r="H3" s="2"/>
       <c r="I3" s="1"/>
@@ -426,13 +438,19 @@
         <v>202511602545</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="C4" s="1" t="n">
         <v>8</v>
       </c>
       <c r="D4" s="1" t="n">
         <v>6</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="F4" s="1" t="n">
+        <v>10</v>
       </c>
       <c r="J4" s="1"/>
     </row>
@@ -441,7 +459,7 @@
         <v>202511603200</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C5" s="1" t="n">
         <v>4</v>
@@ -449,8 +467,12 @@
       <c r="D5" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="E5" s="1"/>
-      <c r="F5" s="2"/>
+      <c r="E5" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>10</v>
+      </c>
       <c r="G5" s="1"/>
       <c r="H5" s="2"/>
       <c r="I5" s="1"/>
@@ -461,13 +483,15 @@
         <v>202511602497</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C6" s="1" t="n">
         <v>10</v>
       </c>
       <c r="D6" s="2"/>
-      <c r="E6" s="1"/>
+      <c r="E6" s="1" t="n">
+        <v>8</v>
+      </c>
       <c r="F6" s="2"/>
       <c r="G6" s="1"/>
       <c r="H6" s="2"/>
@@ -479,7 +503,7 @@
         <v>202511602473</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C7" s="1" t="n">
         <v>8</v>
@@ -487,7 +511,9 @@
       <c r="D7" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="E7" s="1"/>
+      <c r="E7" s="1" t="n">
+        <v>10</v>
+      </c>
       <c r="F7" s="2"/>
       <c r="G7" s="1"/>
       <c r="H7" s="2"/>
@@ -499,7 +525,7 @@
         <v>202511602524</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C8" s="1" t="n">
         <v>0</v>
@@ -507,7 +533,12 @@
       <c r="D8" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="E8" s="1"/>
+      <c r="E8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="1" t="n">
+        <v>0</v>
+      </c>
       <c r="G8" s="1"/>
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
@@ -517,7 +548,7 @@
         <v>202511602491</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C9" s="1" t="n">
         <v>2</v>
@@ -525,8 +556,12 @@
       <c r="D9" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="E9" s="1"/>
-      <c r="F9" s="2"/>
+      <c r="E9" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>6</v>
+      </c>
       <c r="G9" s="1"/>
       <c r="H9" s="2"/>
       <c r="I9" s="1"/>
@@ -537,13 +572,15 @@
         <v>202511602441</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C10" s="1" t="n">
         <v>10</v>
       </c>
       <c r="D10" s="2"/>
-      <c r="E10" s="1"/>
+      <c r="E10" s="1" t="n">
+        <v>10</v>
+      </c>
       <c r="F10" s="2"/>
       <c r="G10" s="1"/>
       <c r="H10" s="2"/>
@@ -555,7 +592,7 @@
         <v>202511602567</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C11" s="1" t="n">
         <v>2</v>
@@ -563,8 +600,12 @@
       <c r="D11" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E11" s="1"/>
-      <c r="F11" s="2"/>
+      <c r="E11" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>10</v>
+      </c>
       <c r="G11" s="1"/>
       <c r="H11" s="2"/>
       <c r="I11" s="1"/>
@@ -575,14 +616,18 @@
         <v>202511602557</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C12" s="1" t="n">
         <v>10</v>
       </c>
       <c r="D12" s="2"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="2"/>
+      <c r="E12" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>8</v>
+      </c>
       <c r="G12" s="1"/>
       <c r="H12" s="2"/>
       <c r="I12" s="1"/>
@@ -593,12 +638,14 @@
         <v>202511602452</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C13" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="E13" s="1"/>
+      <c r="E13" s="1" t="n">
+        <v>10</v>
+      </c>
       <c r="G13" s="1"/>
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
@@ -608,7 +655,7 @@
         <v>202511603204</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C14" s="1" t="n">
         <v>2</v>
@@ -628,7 +675,7 @@
         <v>202511603162</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C15" s="1" t="n">
         <v>2</v>
@@ -646,7 +693,7 @@
         <v>202511602437</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C16" s="1" t="n">
         <v>0</v>
@@ -656,198 +703,234 @@
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
     </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="n">
-        <v>202511602537</v>
+        <v>202511602501</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="D17" s="2"/>
-      <c r="E17" s="1"/>
-      <c r="F17" s="2"/>
+        <v>0</v>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>4</v>
+      </c>
       <c r="G17" s="1"/>
-      <c r="H17" s="2"/>
       <c r="I17" s="1"/>
-      <c r="J17" s="2"/>
+      <c r="J17" s="1"/>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="n">
-        <v>202511602501</v>
+        <v>202511603157</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C18" s="1" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" s="1"/>
-      <c r="G18" s="1"/>
-      <c r="I18" s="1"/>
+        <v>8</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>10</v>
+      </c>
       <c r="J18" s="1"/>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="n">
-        <v>202511603157</v>
+        <v>202511603167</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
+      </c>
+      <c r="C19" s="1" t="n">
+        <v>0</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>8</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="G19" s="1"/>
+      <c r="I19" s="1"/>
       <c r="J19" s="1"/>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="n">
-        <v>202511603167</v>
+        <v>202511602444</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C20" s="1" t="n">
         <v>0</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="E20" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="F20" s="1" t="n">
+        <v>6</v>
+      </c>
       <c r="G20" s="1"/>
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="n">
-        <v>202511602444</v>
+        <v>202511602349</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E21" s="1"/>
+      <c r="F21" s="1" t="n">
+        <v>10</v>
+      </c>
       <c r="G21" s="1"/>
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="n">
-        <v>202511602349</v>
+        <v>202511602536</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="E22" s="1"/>
+        <v>0</v>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="F22" s="1" t="n">
+        <v>6</v>
+      </c>
       <c r="G22" s="1"/>
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="n">
-        <v>202511602536</v>
+        <v>202511602440</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D23" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="E23" s="1"/>
+        <v>6</v>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="F23" s="1" t="n">
+        <v>8</v>
+      </c>
       <c r="G23" s="1"/>
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="n">
-        <v>202511602440</v>
+        <v>202511602492</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="D24" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="E24" s="1"/>
+        <v>10</v>
+      </c>
+      <c r="E24" s="1" t="n">
+        <v>10</v>
+      </c>
       <c r="G24" s="1"/>
       <c r="I24" s="1"/>
       <c r="J24" s="1"/>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="n">
-        <v>202511602492</v>
+        <v>202511602456</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C25" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="E25" s="1"/>
+      <c r="E25" s="1" t="n">
+        <v>10</v>
+      </c>
       <c r="G25" s="1"/>
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="n">
-        <v>202511602456</v>
+        <v>202511603158</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C26" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="E26" s="1"/>
+      <c r="E26" s="1" t="n">
+        <v>10</v>
+      </c>
       <c r="G26" s="1"/>
       <c r="I26" s="1"/>
       <c r="J26" s="1"/>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="n">
-        <v>202511603158</v>
+        <v>202511602455</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="E27" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="D27" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="E27" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="F27" s="1" t="n">
+        <v>6</v>
+      </c>
       <c r="G27" s="1"/>
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="n">
-        <v>202511602455</v>
+        <v>202511602443</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C28" s="1" t="n">
         <v>2</v>
-      </c>
-      <c r="D28" s="1" t="n">
-        <v>6</v>
       </c>
       <c r="E28" s="1"/>
       <c r="G28" s="1"/>
@@ -856,28 +939,33 @@
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="n">
-        <v>202511602443</v>
+        <v>202511602464</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="E29" s="1"/>
+        <v>0</v>
+      </c>
+      <c r="E29" s="1" t="n">
+        <v>0</v>
+      </c>
       <c r="G29" s="1"/>
       <c r="I29" s="1"/>
       <c r="J29" s="1"/>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="n">
-        <v>202511602464</v>
+        <v>202511602459</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>0</v>
+        <v>8</v>
+      </c>
+      <c r="D30" s="1" t="n">
+        <v>4</v>
       </c>
       <c r="E30" s="1"/>
       <c r="G30" s="1"/>
@@ -886,18 +974,21 @@
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="n">
-        <v>202511602459</v>
+        <v>202511602519</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D31" s="1" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E31" s="1"/>
+      <c r="F31" s="1" t="n">
+        <v>2</v>
+      </c>
       <c r="G31" s="1"/>
       <c r="I31" s="1"/>
       <c r="J31" s="1"/>
@@ -907,135 +998,147 @@
         <v>202511602519</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D32" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E32" s="1"/>
+        <v>10</v>
+      </c>
+      <c r="E32" s="1" t="n">
+        <v>10</v>
+      </c>
       <c r="G32" s="1"/>
       <c r="I32" s="1"/>
       <c r="J32" s="1"/>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="n">
-        <v>202511602519</v>
+        <v>202511602569</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="E33" s="1"/>
+        <v>0</v>
+      </c>
+      <c r="D33" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="1" t="n">
+        <v>0</v>
+      </c>
       <c r="G33" s="1"/>
       <c r="I33" s="1"/>
       <c r="J33" s="1"/>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="n">
-        <v>202511602569</v>
+        <v>202511602470</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C34" s="1" t="n">
         <v>0</v>
       </c>
       <c r="D34" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E34" s="1"/>
+        <v>10</v>
+      </c>
+      <c r="E34" s="1" t="n">
+        <v>8</v>
+      </c>
       <c r="G34" s="1"/>
       <c r="I34" s="1"/>
       <c r="J34" s="1"/>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="n">
-        <v>202511602470</v>
+        <v>202511602510</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C35" s="1" t="n">
         <v>0</v>
       </c>
       <c r="D35" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="E35" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="E35" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" s="1" t="n">
+        <v>0</v>
+      </c>
       <c r="G35" s="1"/>
       <c r="I35" s="1"/>
       <c r="J35" s="1"/>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="n">
-        <v>202511602510</v>
+        <v>202511602518</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C36" s="1" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="D36" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="E36" s="1"/>
-      <c r="G36" s="1"/>
-      <c r="I36" s="1"/>
+        <v>6</v>
+      </c>
+      <c r="E36" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="F36" s="1" t="n">
+        <v>2</v>
+      </c>
       <c r="J36" s="1"/>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="n">
-        <v>202511602518</v>
+        <v>202511602530</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
+      </c>
+      <c r="C37" s="1" t="n">
+        <v>4</v>
       </c>
       <c r="D37" s="1" t="n">
-        <v>6</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="E37" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" s="1"/>
+      <c r="I37" s="1"/>
       <c r="J37" s="1"/>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="n">
-        <v>202511602530</v>
+        <v>202511602513</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D38" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="E38" s="1"/>
+        <v>10</v>
+      </c>
+      <c r="E38" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="F38" s="1" t="n">
+        <v>10</v>
+      </c>
       <c r="G38" s="1"/>
       <c r="I38" s="1"/>
       <c r="J38" s="1"/>
-    </row>
-    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="1" t="n">
-        <v>202511602513</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C39" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="D39" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="E39" s="1"/>
-      <c r="G39" s="1"/>
-      <c r="I39" s="1"/>
-      <c r="J39" s="1"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
